--- a/StructureDefinition-inera-ehds-immunization.xlsx
+++ b/StructureDefinition-inera-ehds-immunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
 </t>
   </si>
   <si>
@@ -812,7 +812,7 @@
     <t>The type of vaccine for particular disease or diseases against which the patient has been immunised, or a code for absent/unknown immunization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1168,7 +1168,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1192,7 +1192,7 @@
     <t>SNOMED Route Terms</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1692,13 +1692,13 @@
   <si>
     <t>The particular disease against which the patient has been immunized.
 Additional conformance bindings provided for use for this element in specific (jurisdictional or other) contexts include (these bindings are represented in the StructureDefinition as instances of the [elementdefinition-additionalBinding](http://hl7.org/fhir/tools/StructureDefinition/additional-binding) extension):
-- [targetDiseases-uv-ips](http://hl7.org/fhir/uv/ips/STU2/./ValueSet-target-diseases-uv-ips.html)</t>
+- [targetDiseases-uv-ips](http://hl7.org/fhir/uv/ips/2.0.1/./ValueSet-target-diseases-uv-ips.html)</t>
   </si>
   <si>
     <t>The particular disease or diseases against which the patient has been immunized.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/target-diseases-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/target-diseases-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>

--- a/StructureDefinition-inera-ehds-immunization.xlsx
+++ b/StructureDefinition-inera-ehds-immunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-immunization.xlsx
+++ b/StructureDefinition-inera-ehds-immunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-immunization.xlsx
+++ b/StructureDefinition-inera-ehds-immunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,7 +426,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (vaccinationMedicalRecordHeader.sourceSystemHSAId)</t>
+    <t>Källsystem HSA-id (vaccinationMedicalRecordHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -789,7 +789,7 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
@@ -812,7 +812,7 @@
     <t>The type of vaccine for particular disease or diseases against which the patient has been immunised, or a code for absent/unknown immunization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/vaccines-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1168,7 +1168,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1192,7 +1192,7 @@
     <t>SNOMED Route Terms</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1692,13 +1692,13 @@
   <si>
     <t>The particular disease against which the patient has been immunized.
 Additional conformance bindings provided for use for this element in specific (jurisdictional or other) contexts include (these bindings are represented in the StructureDefinition as instances of the [elementdefinition-additionalBinding](http://hl7.org/fhir/tools/StructureDefinition/additional-binding) extension):
-- [targetDiseases-uv-ips](http://hl7.org/fhir/uv/ips/2.0.1/./ValueSet-target-diseases-uv-ips.html)</t>
+- [targetDiseases-uv-ips](http://hl7.org/fhir/uv/ips/STU2/./ValueSet-target-diseases-uv-ips.html)</t>
   </si>
   <si>
     <t>The particular disease or diseases against which the patient has been immunized.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/target-diseases-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/target-diseases-uv-ips</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
